--- a/results/full_enron_split_summary/enron_ScoreVector_summary.xlsx
+++ b/results/full_enron_split_summary/enron_ScoreVector_summary.xlsx
@@ -2460,142 +2460,142 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.8923±0.0498</t>
+          <t>0.9218±0.0038</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.8730±0.0041</t>
+          <t>0.8480±0.0053</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.8329±0.0058</t>
+          <t>0.7947±0.0069</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.7685±0.0094</t>
+          <t>0.7278±0.0103</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.2508±0.0223</t>
+          <t>0.2695±0.0140</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.1840±0.0159</t>
+          <t>0.1903±0.0165</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.1532±0.0145</t>
+          <t>0.1547±0.0111</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.1273±0.0115</t>
+          <t>0.1261±0.0075</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.5849±0.0528</t>
+          <t>0.6206±0.0080</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0.4974±0.0129</t>
+          <t>0.4743±0.0098</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.3544±0.0151</t>
+          <t>0.3312±0.0130</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.2085±0.0126</t>
+          <t>0.1979±0.0124</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>17.8435±10.2615</t>
+          <t>11.4695±0.5911</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>14.8910±0.5815</t>
+          <t>16.8009±0.7757</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.5007±0.5860</t>
+          <t>20.6508±0.9335</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>21.5944±0.9067</t>
+          <t>25.2487±1.0546</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.6767±0.0601</t>
+          <t>0.7130±0.0039</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.6646±0.0080</t>
+          <t>0.6376±0.0066</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.6180±0.0116</t>
+          <t>0.5520±0.0126</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0.5304±0.0123</t>
+          <t>0.4155±0.0186</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0.2139±0.0219</t>
+          <t>0.2280±0.0109</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.2270±0.0155</t>
+          <t>0.2553±0.0140</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.2566±0.0240</t>
+          <t>0.3261±0.0171</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0.3315±0.0227</t>
+          <t>0.4997±0.0315</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0.1404±0.1185</t>
+          <t>0.0721±0.0034</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>0.1031±0.0044</t>
+          <t>0.1232±0.0059</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.1308±0.0052</t>
+          <t>0.1693±0.0083</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.1806±0.0078</t>
+          <t>0.2349±0.0113</t>
         </is>
       </c>
     </row>
@@ -2632,17 +2632,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.7020±0.0092</t>
+          <t>0.7004±0.0109</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.6336±0.0130</t>
+          <t>0.6322±0.0160</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.5983±0.0192</t>
+          <t>0.5944±0.0174</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.0725±0.0016</t>
+          <t>0.0729±0.0020</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.0697±0.0022</t>
+          <t>0.0695±0.0020</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.0679±0.0017</t>
+          <t>0.0684±0.0019</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2672,17 +2672,17 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.2352±0.0143</t>
+          <t>0.2388±0.0183</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.1868±0.0272</t>
+          <t>0.1854±0.0195</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.1505±0.0284</t>
+          <t>0.1416±0.0228</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2692,17 +2692,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>27.9628±0.5672</t>
+          <t>28.1188±0.7428</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>33.0549±0.8850</t>
+          <t>33.3720±0.9421</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>34.9003±1.2374</t>
+          <t>35.0883±1.1799</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.3619±0.0144</t>
+          <t>0.3585±0.0180</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.2980±0.0236</t>
+          <t>0.2980±0.0212</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.2526±0.0377</t>
+          <t>0.2454±0.0288</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2732,17 +2732,17 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.5531±0.0304</t>
+          <t>0.5582±0.0373</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.6104±0.0586</t>
+          <t>0.6091±0.0450</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.6667±0.0899</t>
+          <t>0.6933±0.0689</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2752,17 +2752,17 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>0.2860±0.0088</t>
+          <t>0.2906±0.0099</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.3563±0.0148</t>
+          <t>0.3594±0.0155</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>0.3930±0.0264</t>
+          <t>0.3973±0.0218</t>
         </is>
       </c>
     </row>
